--- a/docs/files/REPORT_FILTRI/RZV - SITA' STEFANO OSVALDO.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - SITA' STEFANO OSVALDO.xlsx
@@ -684,13 +684,13 @@
         <v>48</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>5214</v>
+        <v>5201</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>3937</v>
+        <v>0</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>3731</v>
+        <v>3662</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -842,19 +842,19 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>751</v>
+        <v>740</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>705</v>
+        <v>688</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>672</v>
+        <v>657</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>1280</v>
+        <v>1256</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>560</v>
+        <v>0</v>
       </c>
       <c r="K11" s="12" t="n">
         <v>258</v>
@@ -863,10 +863,10 @@
         <v>180</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>1030</v>
+        <v>1009</v>
       </c>
       <c r="N11" s="12" t="n">
-        <v>251</v>
+        <v>241</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
@@ -901,19 +901,19 @@
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>531</v>
+        <v>516</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>596</v>
+        <v>579</v>
       </c>
       <c r="I12" s="12" t="n">
         <v>246</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>432</v>
+        <v>0</v>
       </c>
       <c r="K12" s="12" t="n">
         <v>219</v>
@@ -922,10 +922,10 @@
         <v>84</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>440</v>
+        <v>428</v>
       </c>
       <c r="N12" s="12" t="n">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
@@ -960,7 +960,7 @@
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>389</v>
+        <v>396</v>
       </c>
       <c r="G13" s="12" t="n">
         <v>342</v>
@@ -972,7 +972,7 @@
         <v>395</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>343</v>
+        <v>0</v>
       </c>
       <c r="K13" s="12" t="n">
         <v>192</v>
@@ -1019,19 +1019,19 @@
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>206</v>
+        <v>0</v>
       </c>
       <c r="K14" s="12" t="n">
         <v>59</v>
@@ -1040,7 +1040,7 @@
         <v>128</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>561</v>
+        <v>543</v>
       </c>
       <c r="N14" s="12" t="n">
         <v>8</v>
@@ -1078,19 +1078,19 @@
         </is>
       </c>
       <c r="F15" s="12" t="n">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>341</v>
+        <v>336</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>388</v>
+        <v>376</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>569</v>
+        <v>558</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>216</v>
+        <v>0</v>
       </c>
       <c r="K15" s="12" t="n">
         <v>108</v>
@@ -1099,7 +1099,7 @@
         <v>87</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>361</v>
+        <v>348</v>
       </c>
       <c r="N15" s="12" t="n">
         <v>21</v>
@@ -1137,10 +1137,10 @@
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="H16" s="12" t="n">
         <v>20</v>
@@ -1149,7 +1149,7 @@
         <v>45</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>216</v>
+        <v>0</v>
       </c>
       <c r="K16" s="12" t="n">
         <v>82</v>
@@ -1158,10 +1158,10 @@
         <v>78</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>520</v>
+        <v>506</v>
       </c>
       <c r="N16" s="12" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
@@ -1196,10 +1196,10 @@
         </is>
       </c>
       <c r="F17" s="12" t="n">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="H17" s="12" t="n">
         <v>44</v>
@@ -1208,7 +1208,7 @@
         <v>130</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>126</v>
+        <v>0</v>
       </c>
       <c r="K17" s="12" t="n">
         <v>60</v>
@@ -1217,7 +1217,7 @@
         <v>52</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>368</v>
+        <v>361</v>
       </c>
       <c r="N17" s="12" t="n">
         <v>135</v>
@@ -1255,19 +1255,19 @@
         </is>
       </c>
       <c r="F18" s="12" t="n">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>132</v>
+        <v>0</v>
       </c>
       <c r="K18" s="12" t="n">
         <v>44</v>
@@ -1314,19 +1314,19 @@
         </is>
       </c>
       <c r="F19" s="12" t="n">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="I19" s="12" t="n">
         <v>135</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>117</v>
+        <v>0</v>
       </c>
       <c r="K19" s="12" t="n">
         <v>35</v>
@@ -1335,31 +1335,31 @@
         <v>32</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="N19" s="12" t="n">
         <v>44</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>06210</t>
+          <t>15503</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>CARPI</t>
+          <t>IMOLA</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>VIA MANZONI</t>
+          <t>VIA SELICE KM. 2</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -1369,35 +1369,35 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>IACONA GIOVANNI</t>
+          <t>MURGO LORENZO</t>
         </is>
       </c>
       <c r="F20" s="12" t="n">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>122</v>
+        <v>103</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>30</v>
+        <v>286</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>102</v>
+        <v>310</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>121</v>
+        <v>0</v>
       </c>
       <c r="K20" s="12" t="n">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>13</v>
+        <v>44</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>139</v>
+        <v>358</v>
       </c>
       <c r="N20" s="12" t="n">
-        <v>37</v>
+        <v>12</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
@@ -1408,17 +1408,17 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>15503</t>
+          <t>06210</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>IMOLA</t>
+          <t>CARPI</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>VIA SELICE KM. 2</t>
+          <t>VIA MANZONI</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -1428,35 +1428,35 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>MURGO LORENZO</t>
+          <t>IACONA GIOVANNI</t>
         </is>
       </c>
       <c r="F21" s="12" t="n">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>103</v>
+        <v>120</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>287</v>
+        <v>30</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>317</v>
+        <v>102</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>97</v>
+        <v>0</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>44</v>
+        <v>13</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>358</v>
+        <v>136</v>
       </c>
       <c r="N21" s="12" t="n">
-        <v>12</v>
+        <v>37</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
@@ -1467,55 +1467,55 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>05514</t>
+          <t>55557</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>SAN GIOVANNI IN PERSICETO</t>
+          <t>PARMA</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>VIA BOLOGNA 13</t>
+          <t>VIA TRAVERSETOLO</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Tino Vincenzo</t>
+          <t>Nadir Abdel</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>IACONA GIOVANNI</t>
+          <t>BRAVI MATTEO</t>
         </is>
       </c>
       <c r="F22" s="12" t="n">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>71</v>
+        <v>120</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>89</v>
+        <v>122</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>113</v>
+        <v>0</v>
       </c>
       <c r="K22" s="12" t="n">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>219</v>
+        <v>197</v>
       </c>
       <c r="N22" s="12" t="n">
-        <v>31</v>
+        <v>62</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
@@ -1526,55 +1526,55 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>55557</t>
+          <t>05514</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>PARMA</t>
+          <t>SAN GIOVANNI IN PERSICETO</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>VIA TRAVERSETOLO</t>
+          <t>VIA BOLOGNA 13</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t>Tino Vincenzo</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>BRAVI MATTEO</t>
+          <t>IACONA GIOVANNI</t>
         </is>
       </c>
       <c r="F23" s="12" t="n">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>120</v>
+        <v>68</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>125</v>
+        <v>88</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>119</v>
+        <v>0</v>
       </c>
       <c r="K23" s="12" t="n">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>197</v>
+        <v>219</v>
       </c>
       <c r="N23" s="12" t="n">
-        <v>62</v>
+        <v>31</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
@@ -1585,7 +1585,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>54498</t>
+          <t>25556</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -1595,7 +1595,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>VIA FERRARESE 166</t>
+          <t>VIALE DELL'INDUSTRIA 44</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -1609,42 +1609,42 @@
         </is>
       </c>
       <c r="F24" s="12" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>99</v>
+        <v>222</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>55</v>
+        <v>100</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>78</v>
+        <v>257</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="K24" s="12" t="n">
-        <v>41</v>
+        <v>19</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>23</v>
+        <v>54</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>127</v>
+        <v>258</v>
       </c>
       <c r="N24" s="12" t="n">
-        <v>43</v>
+        <v>4</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>25556</t>
+          <t>54498</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
@@ -1654,7 +1654,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>VIALE DELL'INDUSTRIA 44</t>
+          <t>VIA FERRARESE 166</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -1668,35 +1668,35 @@
         </is>
       </c>
       <c r="F25" s="12" t="n">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>226</v>
+        <v>92</v>
       </c>
       <c r="H25" s="12" t="n">
-        <v>103</v>
+        <v>55</v>
       </c>
       <c r="I25" s="12" t="n">
-        <v>257</v>
+        <v>78</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="K25" s="12" t="n">
-        <v>19</v>
+        <v>41</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>54</v>
+        <v>23</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>260</v>
+        <v>127</v>
       </c>
       <c r="N25" s="12" t="n">
-        <v>4</v>
+        <v>43</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1727,19 +1727,19 @@
         </is>
       </c>
       <c r="F26" s="12" t="n">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="J26" s="12" t="n">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="K26" s="12" t="n">
         <v>34</v>
@@ -1748,7 +1748,7 @@
         <v>20</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="N26" s="12" t="n">
         <v>2</v>
@@ -1786,7 +1786,7 @@
         </is>
       </c>
       <c r="F27" s="12" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G27" s="12" t="n">
         <v>73</v>
@@ -1798,7 +1798,7 @@
         <v>13</v>
       </c>
       <c r="J27" s="12" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="K27" s="12" t="n">
         <v>16</v>
@@ -1821,55 +1821,55 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>58000</t>
+          <t>02705</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>MIRANDOLA</t>
+          <t>PODENZANO</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>SS. SUD</t>
+          <t>VIA PAPA GIOVANNI XXIII</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Tino Vincenzo</t>
+          <t>Nadir Abdel</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>CARCIONE PARIDE</t>
+          <t>GIURICIN ANTONIO</t>
         </is>
       </c>
       <c r="F28" s="12" t="n">
         <v>86</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="H28" s="12" t="n">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>104</v>
+        <v>35</v>
       </c>
       <c r="J28" s="12" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="K28" s="12" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="N28" s="12" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
@@ -1880,55 +1880,55 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>02705</t>
+          <t>58000</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>PODENZANO</t>
+          <t>MIRANDOLA</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>VIA PAPA GIOVANNI XXIII</t>
+          <t>SS. SUD</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t>Tino Vincenzo</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>GIURICIN ANTONIO</t>
+          <t>CARCIONE PARIDE</t>
         </is>
       </c>
       <c r="F29" s="12" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>119</v>
+        <v>106</v>
       </c>
       <c r="H29" s="12" t="n">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="I29" s="12" t="n">
-        <v>36</v>
+        <v>102</v>
       </c>
       <c r="J29" s="12" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="K29" s="12" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>26</v>
+        <v>41</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>126</v>
+        <v>116</v>
       </c>
       <c r="N29" s="12" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
@@ -1939,55 +1939,55 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>06403</t>
+          <t>57601</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>GUASTALLA</t>
+          <t>MODENA</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>VIA CISA LIGURE 10</t>
+          <t>VIA VIGNOLESE 1030</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t>Tino Vincenzo</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>BRAVI MATTEO</t>
+          <t>PIETRANTONIO GIULIANO</t>
         </is>
       </c>
       <c r="F30" s="12" t="n">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="H30" s="12" t="n">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="I30" s="12" t="n">
-        <v>24</v>
+        <v>226</v>
       </c>
       <c r="J30" s="12" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="K30" s="12" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="L30" s="12" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="M30" s="12" t="n">
-        <v>108</v>
+        <v>223</v>
       </c>
       <c r="N30" s="12" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
@@ -1998,55 +1998,55 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>57601</t>
+          <t>06403</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>MODENA</t>
+          <t>GUASTALLA</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>VIA VIGNOLESE 1030</t>
+          <t>VIA CISA LIGURE 10</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Tino Vincenzo</t>
+          <t>Nadir Abdel</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>PIETRANTONIO GIULIANO</t>
+          <t>BRAVI MATTEO</t>
         </is>
       </c>
       <c r="F31" s="12" t="n">
         <v>76</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="H31" s="12" t="n">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="I31" s="12" t="n">
-        <v>226</v>
+        <v>24</v>
       </c>
       <c r="J31" s="12" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="K31" s="12" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="L31" s="12" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="M31" s="12" t="n">
-        <v>223</v>
+        <v>107</v>
       </c>
       <c r="N31" s="12" t="n">
-        <v>5</v>
+        <v>48</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
@@ -2057,114 +2057,114 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>56778</t>
+          <t>05588</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>MONTECCHIO EMILIA</t>
+          <t>BOLOGNA</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>S.P PER REGGIO EMILIA 34</t>
+          <t>VIA G. DOZZA, 33</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t>Tino Vincenzo</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>BRAVI MATTEO</t>
+          <t>MURGO LORENZO</t>
         </is>
       </c>
       <c r="F32" s="12" t="n">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>110</v>
+        <v>2</v>
       </c>
       <c r="H32" s="12" t="n">
-        <v>123</v>
+        <v>21</v>
       </c>
       <c r="I32" s="12" t="n">
-        <v>154</v>
+        <v>1</v>
       </c>
       <c r="J32" s="12" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="K32" s="12" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="L32" s="12" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="M32" s="12" t="n">
-        <v>109</v>
+        <v>155</v>
       </c>
       <c r="N32" s="12" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>25534</t>
+          <t>56778</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>BOLOGNA</t>
+          <t>MONTECCHIO EMILIA</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>VIA STALINGRADO 59/4</t>
+          <t>S.P PER REGGIO EMILIA 34</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Tino Vincenzo</t>
+          <t>Nadir Abdel</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>MURGO LORENZO</t>
+          <t>BRAVI MATTEO</t>
         </is>
       </c>
       <c r="F33" s="12" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="H33" s="12" t="n">
-        <v>33</v>
+        <v>122</v>
       </c>
       <c r="I33" s="12" t="n">
-        <v>46</v>
+        <v>153</v>
       </c>
       <c r="J33" s="12" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="K33" s="12" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="L33" s="12" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="M33" s="12" t="n">
-        <v>168</v>
+        <v>109</v>
       </c>
       <c r="N33" s="12" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
@@ -2175,7 +2175,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>05588</t>
+          <t>25534</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -2185,7 +2185,7 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>VIA G. DOZZA, 33</t>
+          <t>VIA STALINGRADO 59/4</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -2199,35 +2199,35 @@
         </is>
       </c>
       <c r="F34" s="12" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>2</v>
+        <v>111</v>
       </c>
       <c r="H34" s="12" t="n">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="I34" s="12" t="n">
-        <v>1</v>
+        <v>46</v>
       </c>
       <c r="J34" s="12" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="K34" s="12" t="n">
+        <v>18</v>
+      </c>
+      <c r="L34" s="12" t="n">
+        <v>17</v>
+      </c>
+      <c r="M34" s="12" t="n">
+        <v>168</v>
+      </c>
+      <c r="N34" s="12" t="n">
         <v>23</v>
       </c>
-      <c r="L34" s="12" t="n">
-        <v>12</v>
-      </c>
-      <c r="M34" s="12" t="n">
-        <v>157</v>
-      </c>
-      <c r="N34" s="12" t="n">
-        <v>1</v>
-      </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -2261,7 +2261,7 @@
         <v>69</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="H35" s="12" t="n">
         <v>25</v>
@@ -2270,7 +2270,7 @@
         <v>103</v>
       </c>
       <c r="J35" s="12" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="K35" s="12" t="n">
         <v>14</v>
@@ -2293,7 +2293,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>05536</t>
+          <t>05530</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -2303,7 +2303,7 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>VIA ALDINI 186</t>
+          <t>VIA MASSARENTI, 221/3</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -2320,150 +2320,150 @@
         <v>64</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>92</v>
+        <v>0</v>
       </c>
       <c r="H36" s="12" t="n">
-        <v>48</v>
+        <v>71</v>
       </c>
       <c r="I36" s="12" t="n">
-        <v>144</v>
+        <v>2</v>
       </c>
       <c r="J36" s="12" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="K36" s="12" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="L36" s="12" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="M36" s="12" t="n">
-        <v>106</v>
+        <v>94</v>
       </c>
       <c r="N36" s="12" t="n">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>06446</t>
+          <t>05536</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>REGGIO NELL'EMILIA</t>
+          <t>BOLOGNA</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>VIA GORIZIA, 25</t>
+          <t>VIA ALDINI 186</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t>Tino Vincenzo</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>CARCIONE PARIDE</t>
+          <t>MURGO LORENZO</t>
         </is>
       </c>
       <c r="F37" s="12" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>6</v>
+        <v>90</v>
       </c>
       <c r="H37" s="12" t="n">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="I37" s="12" t="n">
-        <v>5</v>
+        <v>142</v>
       </c>
       <c r="J37" s="12" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="K37" s="12" t="n">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="L37" s="12" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="M37" s="12" t="n">
-        <v>62</v>
+        <v>102</v>
       </c>
       <c r="N37" s="12" t="n">
-        <v>6</v>
+        <v>41</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>05530</t>
+          <t>06446</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>BOLOGNA</t>
+          <t>REGGIO NELL'EMILIA</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>VIA MASSARENTI, 221/3</t>
+          <t>VIA GORIZIA, 25</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Tino Vincenzo</t>
+          <t>Nadir Abdel</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>MURGO LORENZO</t>
+          <t>CARCIONE PARIDE</t>
         </is>
       </c>
       <c r="F38" s="12" t="n">
         <v>60</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H38" s="12" t="n">
-        <v>75</v>
+        <v>34</v>
       </c>
       <c r="I38" s="12" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J38" s="12" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="K38" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="L38" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="L38" s="12" t="n">
-        <v>14</v>
-      </c>
       <c r="M38" s="12" t="n">
-        <v>97</v>
+        <v>62</v>
       </c>
       <c r="N38" s="12" t="n">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2497,16 +2497,16 @@
         <v>59</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="H39" s="12" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="I39" s="12" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="J39" s="12" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="K39" s="12" t="n">
         <v>15</v>
@@ -2515,10 +2515,10 @@
         <v>19</v>
       </c>
       <c r="M39" s="12" t="n">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="N39" s="12" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
@@ -2553,10 +2553,10 @@
         </is>
       </c>
       <c r="F40" s="12" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="H40" s="12" t="n">
         <v>40</v>
@@ -2565,7 +2565,7 @@
         <v>10</v>
       </c>
       <c r="J40" s="12" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="K40" s="12" t="n">
         <v>16</v>
@@ -2612,10 +2612,10 @@
         </is>
       </c>
       <c r="F41" s="12" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H41" s="12" t="n">
         <v>4</v>
@@ -2624,7 +2624,7 @@
         <v>67</v>
       </c>
       <c r="J41" s="12" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="K41" s="12" t="n">
         <v>11</v>
@@ -2674,7 +2674,7 @@
         <v>42</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H42" s="12" t="n">
         <v>30</v>
@@ -2683,7 +2683,7 @@
         <v>0</v>
       </c>
       <c r="J42" s="12" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="K42" s="12" t="n">
         <v>17</v>
@@ -2706,55 +2706,55 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>55422</t>
+          <t>53490</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>BOLOGNA</t>
+          <t>SANT'ILARIO D'ENZA</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>VIA CRISTOFORO COLOMBO 36</t>
+          <t>VIA FERRARI 38</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>Tino Vincenzo</t>
+          <t>Nadir Abdel</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>MURGO LORENZO</t>
+          <t>IACONA GIOVANNI</t>
         </is>
       </c>
       <c r="F43" s="12" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="G43" s="12" t="n">
-        <v>103</v>
+        <v>61</v>
       </c>
       <c r="H43" s="12" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I43" s="12" t="n">
-        <v>19</v>
+        <v>44</v>
       </c>
       <c r="J43" s="12" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="K43" s="12" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="L43" s="12" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="M43" s="12" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="N43" s="12" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
@@ -2765,76 +2765,76 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>53490</t>
+          <t>54479</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>SANT'ILARIO D'ENZA</t>
+          <t>BENTIVOGLIO</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>VIA FERRARI 38</t>
+          <t>TRASVERSALE DI PIANURA</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t>Tino Vincenzo</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>IACONA GIOVANNI</t>
+          <t>PIETRANTONIO GIULIANO</t>
         </is>
       </c>
       <c r="F44" s="12" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>61</v>
+        <v>3</v>
       </c>
       <c r="H44" s="12" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="I44" s="12" t="n">
-        <v>45</v>
+        <v>3</v>
       </c>
       <c r="J44" s="12" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="K44" s="12" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L44" s="12" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="M44" s="12" t="n">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="N44" s="12" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>54479</t>
+          <t>55422</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>BENTIVOGLIO</t>
+          <t>BOLOGNA</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>TRASVERSALE DI PIANURA</t>
+          <t>VIA CRISTOFORO COLOMBO 36</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -2844,39 +2844,39 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>PIETRANTONIO GIULIANO</t>
+          <t>MURGO LORENZO</t>
         </is>
       </c>
       <c r="F45" s="12" t="n">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="G45" s="12" t="n">
-        <v>3</v>
+        <v>101</v>
       </c>
       <c r="H45" s="12" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="I45" s="12" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="J45" s="12" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="K45" s="12" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="L45" s="12" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="M45" s="12" t="n">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="N45" s="12" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -2910,7 +2910,7 @@
         <v>23</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="H46" s="12" t="n">
         <v>2</v>
@@ -2919,7 +2919,7 @@
         <v>7</v>
       </c>
       <c r="J46" s="12" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="K46" s="12" t="n">
         <v>2</v>
@@ -2966,7 +2966,7 @@
         </is>
       </c>
       <c r="F47" s="12" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G47" s="12" t="n">
         <v>0</v>
@@ -2978,7 +2978,7 @@
         <v>0</v>
       </c>
       <c r="J47" s="12" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="K47" s="12" t="n">
         <v>6</v>
@@ -2994,7 +2994,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -3037,7 +3037,7 @@
         <v>3</v>
       </c>
       <c r="J48" s="12" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="K48" s="12" t="n">
         <v>5</v>
@@ -3096,7 +3096,7 @@
         <v>0</v>
       </c>
       <c r="J49" s="12" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K49" s="12" t="n">
         <v>6</v>
@@ -3142,7 +3142,7 @@
         <v>0</v>
       </c>
       <c r="G50" s="12" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H50" s="12" t="n">
         <v>0</v>
@@ -3222,7 +3222,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -3252,7 +3252,7 @@
         <v>0</v>
       </c>
       <c r="G52" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H52" s="12" t="n">
         <v>0</v>
@@ -3277,7 +3277,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -3317,7 +3317,7 @@
         <v>0</v>
       </c>
       <c r="I53" s="12" t="n">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="J53" s="12" t="n">
         <v>0</v>
@@ -3370,7 +3370,7 @@
         <v>0</v>
       </c>
       <c r="G54" s="12" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H54" s="12" t="n">
         <v>0</v>
@@ -3425,7 +3425,7 @@
         <v>0</v>
       </c>
       <c r="G55" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H55" s="12" t="n">
         <v>0</v>
@@ -3450,7 +3450,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
